--- a/client/public/plantilla-productos.xlsx
+++ b/client/public/plantilla-productos.xlsx
@@ -184,7 +184,7 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>CHIKASTORE</author>
+    <author>ChikakuShop</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
@@ -12812,6 +12812,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
